--- a/layout/CATALOGOS/Restriccion.xlsx
+++ b/layout/CATALOGOS/Restriccion.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29711"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bajaware\Documents\Bitbukec bueno\Mercados\Catalogos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LOCAL\DESA\non-purple-wheel\non-purple-wheel\layout\CATALOGOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6530C99A-D47F-4932-9A22-D341EBA47622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{89A6DE3F-686D-4B78-89E1-C1DAC1182FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{E5D7A69F-5C38-488D-8AAA-B2C564691C50}"/>
+    <workbookView xWindow="7020" yWindow="2292" windowWidth="17280" windowHeight="10500" xr2:uid="{53DC78E7-50CA-465F-AA5F-ADCCF70DE597}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Restriccion" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,15 +31,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
-  <si>
-    <t>Restriccion</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>CLAVE</t>
   </si>
@@ -90,19 +90,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="14"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -123,18 +117,12 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -169,29 +157,23 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal_CATALOGOS" xfId="1" xr:uid="{3627F2EF-2492-43A2-B6C9-DB9F9F5F8DD1}"/>
+    <cellStyle name="Normal_CATALOGOS" xfId="1" xr:uid="{B1AEB21A-5806-4BB5-802C-1458B07D0B52}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -207,7 +189,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -217,39 +199,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -301,7 +283,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -412,13 +394,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -427,6 +402,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -491,312 +473,93 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAD59829-891B-4284-818C-2AA36E042767}">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EC58346-3E3D-41A6-B0EF-7F8FB5464E25}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="42.42578125" customWidth="1"/>
+    <col min="2" max="2" width="58.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.600000000000001">
+    <row r="1" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="2" spans="1:2" ht="29.1">
-      <c r="A2" s="3" t="s">
-        <v>1</v>
+    <row r="2" spans="1:2" ht="90" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="26.45">
-      <c r="A3" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="5" t="s">
+    <row r="3" spans="1:2" ht="90" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="B3" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="4" spans="1:2" ht="52.5">
-      <c r="A4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="5" t="s">
+    <row r="4" spans="1:2" ht="90" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="B4" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:2" ht="26.45">
-      <c r="A5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="5" t="s">
+    <row r="5" spans="1:2" ht="90" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="B5" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="6" spans="1:2" ht="26.45">
-      <c r="A6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="5" t="s">
+    <row r="6" spans="1:2" ht="90" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="65.45">
-      <c r="A7" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cf35dce2-b600-471d-a6b0-9e8301b7851b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3de82841-ffbb-418b-a888-39c303bacd30" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101003EADB6AB950C774BBB9F1C75E500B284" ma:contentTypeVersion="12" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="101bf262c701ad3b79067f76f13f8957">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cf35dce2-b600-471d-a6b0-9e8301b7851b" xmlns:ns3="3de82841-ffbb-418b-a888-39c303bacd30" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a75b904d2a00e23a3c27f0f1b23bc34b" ns2:_="" ns3:_="">
-    <xsd:import namespace="cf35dce2-b600-471d-a6b0-9e8301b7851b"/>
-    <xsd:import namespace="3de82841-ffbb-418b-a888-39c303bacd30"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="cf35dce2-b600-471d-a6b0-9e8301b7851b" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="7ede4d0a-0766-4f1c-ae6e-d82e4c79f9cb" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="19" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3de82841-ffbb-418b-a888-39c303bacd30" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{f69b061e-8b27-4b88-9ef3-0b189eff6be7}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3de82841-ffbb-418b-a888-39c303bacd30">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F728C2E-D0E5-42EC-8361-7B31652263A9}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6075D621-2743-4618-AA5F-47EDCCD66738}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8521DC97-AA1B-47F5-B4B1-D2D924323461}"/>
 </file>